--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07T12:20:42</t>
+    <t xml:space="preserve">2026-09-08T11:09:39</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -145,6 +145,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -160,7 +178,70 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator / DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Student</t>
@@ -244,7 +325,22 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
@@ -262,24 +358,6 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -319,9 +397,6 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
@@ -331,6 +406,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator - 243425</t>
   </si>
   <si>
@@ -346,114 +436,153 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -478,6 +607,15 @@
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Israel</t>
   </si>
   <si>
@@ -499,27 +637,12 @@
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -532,37 +655,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -574,9 +679,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -604,40 +706,58 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -646,40 +766,19 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -688,10 +787,10 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
@@ -840,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -848,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -864,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10">
@@ -946,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -962,7 +1061,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -996,7 +1095,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1015,7 +1114,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1072,7 +1171,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1104,22 +1203,22 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -1127,19 +1226,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1165,25 +1264,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3">
-        <v>70</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -1197,25 +1296,25 @@
         <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>96</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1223,31 +1322,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>96</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>61</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1255,31 +1354,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1287,31 +1386,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>47</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -1319,31 +1418,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -1351,31 +1450,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1383,31 +1482,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -1415,31 +1514,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -1447,31 +1546,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -1479,31 +1578,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -1511,31 +1610,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1543,31 +1642,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1575,31 +1674,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>27</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1607,31 +1706,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>44</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>27</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1639,31 +1738,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>44</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
@@ -1671,31 +1770,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>40</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1703,31 +1802,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>36</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1735,31 +1834,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
@@ -1767,31 +1866,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -1799,31 +1898,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
@@ -1831,31 +1930,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +1992,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -1908,7 +2007,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -1923,22 +2022,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -1952,7 +2051,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -1961,7 +2060,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -1973,7 +2072,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1987,51 +2086,51 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2043,7 +2142,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2054,31 +2153,31 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3">
-        <v>70</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K5" s="3">
-        <v>18</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -2089,728 +2188,728 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>96</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="G6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>96</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>61</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>47</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K9" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="K11" s="3">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K15" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3">
+        <v>46</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K18" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>44</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>27</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>44</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>40</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>23</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K21" s="3">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K22" s="3">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K23" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="K26" s="3">
         <v>12</v>
@@ -2818,109 +2917,424 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K28" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="3">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K30" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K32" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K33" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>10</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K36" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E37" s="3">
+        <v>4</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K29" s="3">
-        <v>40</v>
+      <c r="I38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K38" s="3">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K38"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -2950,6 +3364,15 @@
     <hyperlink ref="I27" r:id="rId26"/>
     <hyperlink ref="I28" r:id="rId27"/>
     <hyperlink ref="I29" r:id="rId28"/>
+    <hyperlink ref="I30" r:id="rId29"/>
+    <hyperlink ref="I31" r:id="rId30"/>
+    <hyperlink ref="I32" r:id="rId31"/>
+    <hyperlink ref="I33" r:id="rId32"/>
+    <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
+    <hyperlink ref="I38" r:id="rId37"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -2957,11 +3380,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -2980,10 +3403,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -2991,31 +3414,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>96</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>96</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>88</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3030,178 +3525,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3221,10 +3716,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3232,10 +3727,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -3243,10 +3738,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -3254,10 +3749,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -3268,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -3279,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3300,13 +3795,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2">
@@ -3317,7 +3812,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3326,22 +3821,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08T11:09:39</t>
+    <t xml:space="preserve">2026-09-09T11:14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,19 +91,22 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+    <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">By source</t>
@@ -163,325 +166,403 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
     <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Enterprise Systems Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-enterprise-systems-support-engineer-at-cross-river-4464614783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator / DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
   </si>
   <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
     <t xml:space="preserve">Support Engineer</t>
@@ -496,165 +577,204 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratasys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory, Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -670,6 +790,51 @@
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (37425)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37425-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464324940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier I Technical Support Specialist — Smart Cooler Vending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-i-technical-support-specialist-%E2%80%94-smart-cooler-vending-at-jobgether-4463227567</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -679,6 +844,54 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Networks Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-impact-networks-group-4464458660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464346260</t>
+  </si>
+  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -700,18 +913,15 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -721,9 +931,6 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -736,6 +943,18 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -748,37 +967,28 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -787,19 +997,22 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -939,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +1160,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -963,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10">
@@ -1045,7 +1258,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1053,7 +1266,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1274,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1069,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1081,28 +1294,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>32</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1116,7 +1337,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1127,34 +1348,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1162,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>27</v>
@@ -1177,16 +1398,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1194,31 +1415,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1226,31 +1447,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1264,10 +1485,10 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1276,7 +1497,7 @@
         <v>62</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>63</v>
@@ -1296,25 +1517,25 @@
         <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
         <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1322,31 +1543,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>96</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1354,31 +1575,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1386,13 +1607,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1401,16 +1622,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -1418,31 +1639,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1450,13 +1671,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1465,16 +1686,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1482,31 +1703,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
         <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1514,31 +1735,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
         <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1546,31 +1767,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
         <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1578,31 +1799,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
         <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1610,31 +1831,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -1642,31 +1863,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
         <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -1674,31 +1895,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1706,31 +1927,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1738,31 +1959,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1770,31 +1991,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -1802,31 +2023,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1834,31 +2055,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -1866,31 +2087,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -1898,31 +2119,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -1930,31 +2151,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1993,8 +2214,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2007,48 +2228,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -2057,92 +2278,92 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -2153,10 +2374,10 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2165,10 +2386,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>63</v>
@@ -2177,7 +2398,7 @@
         <v>64</v>
       </c>
       <c r="K5" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -2188,112 +2409,112 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
         <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>96</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2302,68 +2523,68 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K9" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2372,969 +2593,1599 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
         <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
         <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
         <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
         <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
         <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
         <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="K21" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="K25" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="K26" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="K27" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="K28" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K29" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="K33" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>206</v>
+        <v>52</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K34" s="3">
         <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>10</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K34" s="3">
-        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="K35" s="3">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K36" s="3">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="K37" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K38" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="C39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K40" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K42" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K43" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E44" s="3">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K45" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K46" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="3">
-        <v>41</v>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K48" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K49" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="3">
+        <v>4</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K51" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K52" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K53" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K56" s="3">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K56"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3373,6 +4224,24 @@
     <hyperlink ref="I36" r:id="rId35"/>
     <hyperlink ref="I37" r:id="rId36"/>
     <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
+    <hyperlink ref="I46" r:id="rId45"/>
+    <hyperlink ref="I47" r:id="rId46"/>
+    <hyperlink ref="I48" r:id="rId47"/>
+    <hyperlink ref="I49" r:id="rId48"/>
+    <hyperlink ref="I50" r:id="rId49"/>
+    <hyperlink ref="I51" r:id="rId50"/>
+    <hyperlink ref="I52" r:id="rId51"/>
+    <hyperlink ref="I53" r:id="rId52"/>
+    <hyperlink ref="I54" r:id="rId53"/>
+    <hyperlink ref="I55" r:id="rId54"/>
+    <hyperlink ref="I56" r:id="rId55"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3380,9 +4249,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3391,126 +4260,222 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>206</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3525,178 +4490,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3713,13 +4678,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
@@ -3727,10 +4692,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
@@ -3738,10 +4703,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4">
@@ -3749,10 +4714,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
@@ -3760,10 +4725,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
@@ -3774,7 +4739,18 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -3792,51 +4768,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09T11:14:16</t>
+    <t xml:space="preserve">2026-09-10T11:10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -118,6 +118,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -184,18 +187,6 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -229,732 +220,615 @@
     <t xml:space="preserve">2026-09-08</t>
   </si>
   <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratasys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBS-HR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nbs-hr-4463014591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4463025828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Enterprise Systems Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-enterprise-systems-support-engineer-at-cross-river-4464614783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratasys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (37425)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37425-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464324940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier I Technical Support Specialist — Smart Cooler Vending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-i-technical-support-specialist-%E2%80%94-smart-cooler-vending-at-jobgether-4463227567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Networks Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-impact-networks-group-4464458660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464346260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -967,28 +841,25 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -997,12 +868,12 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
@@ -1025,9 +896,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1020,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1160,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1168,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1176,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10">
@@ -1258,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1266,7 +1134,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1274,7 +1142,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1316,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1324,7 +1192,15 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1213,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1348,34 +1224,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1383,13 +1259,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>27</v>
@@ -1398,16 +1274,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1415,13 +1291,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>30</v>
@@ -1430,16 +1306,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1447,31 +1323,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1479,31 +1355,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1511,31 +1387,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1543,31 +1419,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1575,31 +1451,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1607,31 +1483,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1639,31 +1515,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1671,31 +1547,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1703,31 +1579,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1735,31 +1611,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1767,31 +1643,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1799,31 +1675,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -1831,31 +1707,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1863,31 +1739,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -1895,31 +1771,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1927,31 +1803,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="3">
-        <v>46</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1959,31 +1835,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1991,19 +1867,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>147</v>
@@ -2015,7 +1891,7 @@
         <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -2029,25 +1905,25 @@
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -2055,31 +1931,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2087,19 +1963,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
@@ -2125,25 +2001,25 @@
         <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2151,31 +2027,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2214,8 +2090,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2228,48 +2104,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -2278,33 +2154,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -2313,640 +2189,640 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K11" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="K15" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="K17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>32</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="3">
-        <v>46</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2955,10 +2831,10 @@
         <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K21" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2969,89 +2845,89 @@
         <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K22" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K23" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -3063,7 +2939,7 @@
         <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -3074,474 +2950,474 @@
         <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="K27" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K28" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>94</v>
       </c>
       <c r="K31" s="3">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="K32" s="3">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>47</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="K34" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K35" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="K36" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>229</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
@@ -3550,642 +3426,185 @@
         <v>230</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="K38" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>159</v>
+        <v>231</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="K39" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K40" s="3">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="K41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>243</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>106</v>
+        <v>248</v>
       </c>
       <c r="K42" s="3">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
-        <v>9</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>248</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>138</v>
+        <v>253</v>
       </c>
       <c r="K43" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K44" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" s="3">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>6</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K46" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K48" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K49" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>6</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="3">
-        <v>4</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K51" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K52" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>3</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K53" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K55" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="3">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K56" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K56"/>
+  <autoFilter ref="A1:K43"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4229,19 +3648,6 @@
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
     <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
-    <hyperlink ref="I46" r:id="rId45"/>
-    <hyperlink ref="I47" r:id="rId46"/>
-    <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
-    <hyperlink ref="I50" r:id="rId49"/>
-    <hyperlink ref="I51" r:id="rId50"/>
-    <hyperlink ref="I52" r:id="rId51"/>
-    <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4250,232 +3656,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4490,178 +3800,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>305</v>
+        <v>234</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4678,13 +3988,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2">
@@ -4692,10 +4002,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -4703,10 +4013,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -4714,10 +4024,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -4728,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
@@ -4739,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
@@ -4750,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -4768,16 +4078,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2">
@@ -4785,10 +4095,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4797,22 +4107,22 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10T11:10:19</t>
+    <t xml:space="preserve">2026-09-11T11:09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -187,355 +187,352 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratasys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
     <t xml:space="preserve">Title</t>
@@ -556,45 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -604,24 +562,12 @@
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -658,31 +604,13 @@
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">System administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBS-HR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nbs-hr-4463014591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -724,30 +652,6 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4463025828</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -760,9 +664,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Student Success Coach</t>
   </si>
   <si>
@@ -790,31 +691,43 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -829,22 +742,10 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -853,13 +754,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -871,19 +775,19 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1020,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1036,7 +940,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1044,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10">
@@ -1126,7 +1030,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1134,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1142,7 +1046,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1184,7 +1088,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1192,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1200,7 +1104,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1212,7 +1116,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1268,7 +1172,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1300,7 +1204,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1347,7 +1251,7 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1355,31 +1259,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>83</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3">
-        <v>96</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1387,31 +1291,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1419,31 +1323,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>79</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3">
-        <v>83</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1451,19 +1355,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1475,7 +1379,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1483,13 +1387,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -1498,16 +1402,16 @@
         <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1515,31 +1419,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
         <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1547,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>95</v>
@@ -1556,10 +1460,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1571,7 +1475,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1579,31 +1483,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1611,31 +1515,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1643,31 +1547,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1675,31 +1579,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
         <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -1707,31 +1611,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1643,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1763,7 +1667,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1771,28 +1675,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>28</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3">
-        <v>39</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>50</v>
@@ -1803,31 +1707,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1835,31 +1739,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>28</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1873,25 +1777,25 @@
         <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1899,31 +1803,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1931,13 +1835,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1955,7 +1859,7 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1963,31 +1867,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -1995,31 +1899,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
@@ -2033,25 +1937,25 @@
         <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>20</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +1994,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2104,7 +2008,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2119,22 +2023,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2148,7 +2052,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2157,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2169,7 +2073,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2087,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2192,7 +2096,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2204,7 +2108,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2227,7 +2131,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2236,138 +2140,138 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>83</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3">
-        <v>96</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>79</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3">
-        <v>83</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2376,21 +2280,21 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
@@ -2399,62 +2303,62 @@
         <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
         <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="K10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>95</v>
@@ -2463,16 +2367,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2481,208 +2385,208 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
         <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K15" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2691,115 +2595,115 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="3">
-        <v>39</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="3">
         <v>28</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="3">
-        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -2810,77 +2714,77 @@
         <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="K21" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2892,7 +2796,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2901,80 +2805,80 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K24" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="K25" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2985,66 +2889,66 @@
         <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>20</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="K26" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -3055,556 +2959,311 @@
         <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="3">
-        <v>13</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="K28" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>12</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="K29" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>10</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="3">
-        <v>9</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="K32" s="3">
-        <v>15</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="3">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>6</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="K36" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K37" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K38" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>3</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="K40" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="3">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="K42" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="K43" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3641,13 +3300,6 @@
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
     <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
-    <hyperlink ref="I38" r:id="rId37"/>
-    <hyperlink ref="I39" r:id="rId38"/>
-    <hyperlink ref="I40" r:id="rId39"/>
-    <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3655,11 +3307,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="59" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3678,10 +3330,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3689,33 +3341,33 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -3724,68 +3376,20 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3793,185 +3397,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3991,10 +3595,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
@@ -4002,10 +3606,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -4013,10 +3617,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -4024,10 +3628,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
@@ -4038,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -4049,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -4060,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4081,13 +3685,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -4095,10 +3699,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4107,10 +3711,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4119,10 +3723,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-11T11:09:59</t>
+    <t xml:space="preserve">2026-09-13T11:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,15 +100,15 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -232,462 +232,447 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CertifyOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-hillcrest-labs-acquired-by-ceva-4457713529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
@@ -700,15 +685,15 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -718,28 +703,34 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -748,12 +739,6 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
@@ -781,13 +766,13 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -924,7 +909,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -932,7 +917,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +933,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>513</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10">
@@ -1030,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1038,7 +1023,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1054,7 +1039,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1104,7 +1089,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1101,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1204,7 +1189,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1335,19 +1320,19 @@
         <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1355,31 +1340,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>68</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1393,25 +1378,25 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>68</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1419,19 +1404,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1492,10 +1477,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -1524,10 +1509,10 @@
         <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>109</v>
@@ -1571,7 +1556,7 @@
         <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1579,31 +1564,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>39</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1611,28 +1596,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>28</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>50</v>
@@ -1643,31 +1628,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -1675,13 +1660,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1690,16 +1675,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1707,31 +1692,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1739,13 +1724,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1754,16 +1739,16 @@
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -1771,31 +1756,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1803,13 +1788,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1818,16 +1803,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
@@ -1835,13 +1820,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1850,16 +1835,16 @@
         <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -1867,10 +1852,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>53</v>
@@ -1882,16 +1867,16 @@
         <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
@@ -1899,13 +1884,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1914,16 +1899,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1931,13 +1916,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -1946,16 +1931,16 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1994,7 +1979,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2008,7 +1993,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2023,22 +2008,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2061,7 +2046,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2073,7 +2058,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2087,7 +2072,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2096,7 +2081,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2108,7 +2093,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2131,7 +2116,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2143,7 +2128,7 @@
         <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2166,7 +2151,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>33</v>
@@ -2178,7 +2163,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -2201,7 +2186,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2213,7 +2198,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -2230,60 +2215,60 @@
         <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>68</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2294,54 +2279,54 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>68</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2353,7 +2338,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2376,7 +2361,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2388,7 +2373,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2402,16 +2387,16 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2423,7 +2408,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2437,16 +2422,16 @@
         <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2458,7 +2443,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2481,7 +2466,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2490,126 +2475,126 @@
         <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="K15" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>28</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K17" s="3">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2618,68 +2603,68 @@
         <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>28</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>27</v>
@@ -2688,68 +2673,68 @@
         <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K20" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="K21" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2758,33 +2743,33 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="K22" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2793,30 +2778,30 @@
         <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>53</v>
@@ -2828,33 +2813,33 @@
         <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2863,33 +2848,33 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -2898,33 +2883,33 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K26" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>27</v>
@@ -2933,62 +2918,62 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K28" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>46</v>
@@ -3003,33 +2988,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K29" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3038,33 +3023,33 @@
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3073,27 +3058,27 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>62</v>
@@ -3108,103 +3093,101 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K32" s="3">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="K33" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3214,56 +3197,23 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="K35" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="K36" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K35"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3299,7 +3249,6 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3307,11 +3256,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="59" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3330,10 +3279,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3341,55 +3290,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3404,178 +3329,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3">
         <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3595,10 +3520,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -3606,10 +3531,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -3617,10 +3542,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -3631,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -3639,10 +3564,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -3653,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -3664,7 +3589,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3685,13 +3610,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3702,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3714,7 +3639,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3723,10 +3648,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-14T12:35:07</t>
+    <t xml:space="preserve">2026-09-15T11:38:01</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -199,7 +199,421 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia/Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Monitoring Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-monitoring-specialist-at-confidential-careers-4465521603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
     <t xml:space="preserve">Nice</t>
@@ -208,444 +622,6 @@
     <t xml:space="preserve">Israel - Raanana</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-peax-dorcom-4464776806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -727,15 +703,15 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -754,16 +730,22 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -772,22 +754,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -948,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -972,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10">
@@ -1054,7 +1030,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1062,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1112,7 +1088,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1120,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1289,25 +1265,25 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1315,19 +1291,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1339,7 +1315,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1347,31 +1323,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>68</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1385,25 +1361,25 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>68</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1411,19 +1387,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1484,10 +1460,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1516,10 +1492,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -1548,10 +1524,10 @@
         <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>109</v>
@@ -1563,7 +1539,7 @@
         <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1571,31 +1547,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1603,31 +1579,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>39</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1635,10 +1611,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1647,19 +1623,19 @@
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1667,31 +1643,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -1699,31 +1675,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1731,31 +1707,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1769,25 +1745,25 @@
         <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1795,31 +1771,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1827,13 +1803,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1842,16 +1818,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1859,31 +1835,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -1891,31 +1867,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1923,31 +1899,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
@@ -1955,31 +1931,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +2008,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2047,22 +2023,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2085,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2097,7 +2073,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2120,7 +2096,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2132,7 +2108,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2155,7 +2131,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2167,7 +2143,7 @@
         <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2178,54 +2154,54 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>80</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>83</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2234,45 +2210,45 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>68</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>70</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K7" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2283,54 +2259,54 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>61</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>68</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K8" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2342,7 +2318,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2365,7 +2341,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2377,7 +2353,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2391,16 +2367,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2412,7 +2388,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -2426,16 +2402,16 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2447,7 +2423,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2461,16 +2437,16 @@
         <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2479,88 +2455,88 @@
         <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K14" s="3">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>32</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>39</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K15" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2569,130 +2545,130 @@
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K18" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>28</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -2703,77 +2679,77 @@
         <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K20" s="3">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2782,547 +2758,477 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K22" s="3">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>24</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="K23" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="K24" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K27" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>12</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="K28" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="3">
-        <v>9</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K30" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="K31" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K34" s="3">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="K35" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K36" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="K37" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K35"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3358,8 +3264,6 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3367,11 +3271,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3390,10 +3294,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3401,48 +3305,48 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3457,185 +3361,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3655,10 +3559,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
@@ -3666,10 +3570,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -3677,10 +3581,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -3691,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
@@ -3702,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -3713,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -3724,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3745,13 +3649,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -3759,10 +3663,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3771,10 +3675,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3786,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15T11:38:01</t>
+    <t xml:space="preserve">2026-09-16T11:24:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,6 +187,24 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -262,6 +280,21 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -454,34 +487,28 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
   </si>
   <si>
     <t xml:space="preserve">Oracle</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
@@ -508,6 +535,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Israel</t>
   </si>
   <si>
@@ -535,24 +580,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -589,30 +616,18 @@
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Monitoring Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-monitoring-specialist-at-confidential-careers-4465521603</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-15</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -703,15 +718,15 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -754,16 +769,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -924,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -948,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10">
@@ -1030,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1088,7 +1103,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1233,7 +1248,7 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>25</v>
@@ -1242,16 +1257,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1259,10 +1274,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1271,19 +1286,19 @@
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1291,19 +1306,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1315,7 +1330,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1323,31 +1338,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1361,25 +1376,25 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1387,19 +1402,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1428,10 +1443,10 @@
         <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1443,7 +1458,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1451,31 +1466,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3">
-        <v>46</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1483,31 +1498,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1515,31 +1530,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>39</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1553,25 +1568,25 @@
         <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1579,31 +1594,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1611,10 +1626,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1623,19 +1638,19 @@
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1643,31 +1658,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1675,31 +1690,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1707,31 +1722,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1745,25 +1760,25 @@
         <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1771,31 +1786,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>27</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1803,13 +1818,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1818,16 +1833,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1835,19 +1850,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>158</v>
@@ -1867,31 +1882,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -1899,31 +1914,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26">
@@ -1931,31 +1946,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2088,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -2108,7 +2123,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2119,7 +2134,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
@@ -2128,7 +2143,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>178</v>
@@ -2137,21 +2152,21 @@
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2160,10 +2175,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>178</v>
@@ -2172,30 +2187,30 @@
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K5" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
@@ -2210,45 +2225,45 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -2259,48 +2274,48 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
@@ -2332,10 +2347,10 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
@@ -2350,30 +2365,30 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="K10" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>178</v>
@@ -2382,33 +2397,33 @@
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K11" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>178</v>
@@ -2417,33 +2432,33 @@
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K12" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>39</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>178</v>
@@ -2452,13 +2467,13 @@
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -2469,16 +2484,16 @@
         <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>178</v>
@@ -2487,33 +2502,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>178</v>
@@ -2522,21 +2537,21 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2545,10 +2560,10 @@
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>178</v>
@@ -2557,33 +2572,33 @@
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>178</v>
@@ -2592,33 +2607,33 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>178</v>
@@ -2627,33 +2642,33 @@
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>178</v>
@@ -2662,13 +2677,13 @@
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="K19" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -2679,16 +2694,16 @@
         <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>178</v>
@@ -2697,33 +2712,33 @@
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="K20" s="3">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>178</v>
@@ -2732,24 +2747,24 @@
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="K21" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2758,7 +2773,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>178</v>
@@ -2767,30 +2782,30 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>158</v>
@@ -2808,27 +2823,27 @@
         <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>178</v>
@@ -2837,33 +2852,33 @@
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>178</v>
@@ -2872,48 +2887,48 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="K25" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="K26" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2924,13 +2939,13 @@
         <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>181</v>
@@ -2945,10 +2960,10 @@
         <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="K27" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -2956,54 +2971,54 @@
         <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="K28" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>178</v>
@@ -3012,33 +3027,33 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>47</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>178</v>
@@ -3050,21 +3065,21 @@
         <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3073,7 +3088,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>178</v>
@@ -3085,80 +3100,80 @@
         <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>90</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K32" s="3">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="K33" s="3">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
@@ -3172,26 +3187,28 @@
         <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="K34" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3215,7 +3232,7 @@
         <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>218</v>
@@ -3224,11 +3241,44 @@
         <v>219</v>
       </c>
       <c r="K35" s="3">
-        <v>41</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K36" s="3">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K35"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3264,6 +3314,7 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3271,11 +3322,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3305,48 +3356,48 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>195</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>195</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3361,185 +3412,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3559,10 +3610,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3570,10 +3621,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -3584,7 +3635,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -3595,7 +3646,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -3606,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -3617,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -3628,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3649,13 +3700,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -3666,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3678,7 +3729,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3690,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -5,16 +5,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
-    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
-    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
-    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
+    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
+    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16T11:24:46</t>
+    <t xml:space="preserve">2026-09-17T11:33:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -151,6 +150,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
   </si>
   <si>
@@ -187,24 +204,6 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -382,39 +381,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -424,18 +411,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -508,7 +483,10 @@
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
@@ -535,6 +513,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia/Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -553,33 +558,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia/Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -601,66 +579,57 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -700,33 +669,33 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -769,16 +738,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -939,7 +908,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +916,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +924,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -963,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10">
@@ -1045,7 +1014,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1103,7 +1072,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1187,7 +1156,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1219,7 +1188,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1251,7 +1220,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1280,7 +1249,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1298,7 +1267,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -1312,7 +1281,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1362,7 +1331,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -1408,7 +1377,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1458,7 +1427,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1618,7 +1587,7 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1632,25 +1601,25 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1658,19 +1627,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1682,7 +1651,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1690,19 +1659,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1714,7 +1683,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -1722,31 +1691,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1754,31 +1723,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1786,31 +1755,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1818,13 +1787,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1833,16 +1802,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1850,31 +1819,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -1882,10 +1851,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>90</v>
@@ -1894,19 +1863,19 @@
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1914,31 +1883,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
@@ -1946,31 +1915,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2023,7 +1992,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2038,22 +2007,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2067,7 +2036,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2076,7 +2045,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2088,7 +2057,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2102,7 +2071,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2111,7 +2080,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2123,7 +2092,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2137,7 +2106,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2146,7 +2115,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2158,7 +2127,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2169,7 +2138,7 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2181,7 +2150,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2190,10 +2159,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2204,7 +2173,7 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2216,7 +2185,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2228,7 +2197,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2220,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2260,10 +2229,10 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -2286,7 +2255,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2298,7 +2267,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2309,7 +2278,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2321,7 +2290,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2333,7 +2302,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2356,7 +2325,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2365,10 +2334,10 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2391,7 +2360,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2403,7 +2372,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -2426,7 +2395,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2438,7 +2407,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2461,7 +2430,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2473,7 +2442,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -2496,7 +2465,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2508,7 +2477,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2531,7 +2500,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2540,10 +2509,10 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2554,54 +2523,54 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2610,33 +2579,33 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2645,126 +2614,126 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="K18" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="K19" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K20" s="3">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2773,65 +2742,65 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K23" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>90</v>
@@ -2840,165 +2809,165 @@
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="K24" s="3">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="K25" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="K27" s="3">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -3009,19 +2978,19 @@
         <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3030,255 +2999,150 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K36" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K33"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3312,104 +3176,11 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3">
-        <v>100</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G3"/>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-  </hyperlinks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3419,185 +3190,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3610,10 +3381,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -3621,10 +3392,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -3635,7 +3406,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -3646,7 +3417,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -3657,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -3668,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -3679,14 +3450,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3700,13 +3471,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3714,10 +3485,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3726,10 +3497,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3741,7 +3512,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17T11:33:16</t>
+    <t xml:space="preserve">2026-09-18T11:06:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -381,6 +381,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator 7992</t>
   </si>
   <si>
@@ -399,9 +414,6 @@
     <t xml:space="preserve">2026-09-14</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -525,13 +537,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Optimove</t>
   </si>
   <si>
-    <t xml:space="preserve">Estonia/Scotland</t>
+    <t xml:space="preserve">Estonia</t>
   </si>
   <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
@@ -540,24 +570,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -687,13 +699,13 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Python</t>
@@ -908,7 +920,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1014,7 +1026,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1072,7 +1084,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1601,25 +1613,25 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1627,19 +1639,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1651,7 +1663,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1659,19 +1671,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1683,7 +1695,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -1691,13 +1703,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1706,16 +1718,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1723,31 +1735,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1755,13 +1767,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1787,13 +1799,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1802,16 +1814,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1819,31 +1831,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>24</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -1851,19 +1863,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>164</v>
@@ -1875,7 +1887,7 @@
         <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
@@ -1883,13 +1895,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1907,7 +1919,7 @@
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -1921,25 +1933,25 @@
         <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1992,7 +2004,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2007,22 +2019,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -2045,7 +2057,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2057,7 +2069,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2080,7 +2092,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2092,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2115,7 +2127,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2127,7 +2139,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2150,7 +2162,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2162,7 +2174,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -2185,7 +2197,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2197,7 +2209,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -2220,7 +2232,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2232,7 +2244,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -2255,7 +2267,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2267,7 +2279,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2290,7 +2302,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2302,7 +2314,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2325,7 +2337,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2337,7 +2349,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2360,7 +2372,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2372,7 +2384,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2395,7 +2407,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2407,7 +2419,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2430,7 +2442,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2442,7 +2454,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -2465,7 +2477,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2477,7 +2489,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2500,7 +2512,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,7 +2524,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2523,54 +2535,54 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K16" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2579,33 +2591,33 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2614,21 +2626,21 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2637,68 +2649,68 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="K19" s="3">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K20" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,7 +2722,7 @@
         <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2722,18 +2734,18 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2742,80 +2754,80 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="K22" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>24</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="3">
-        <v>23</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2824,21 +2836,21 @@
         <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2850,7 +2862,7 @@
         <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2859,10 +2871,10 @@
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -2873,66 +2885,66 @@
         <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="3">
-        <v>10</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K27" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2940,48 +2952,48 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
@@ -2990,7 +3002,7 @@
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -2999,124 +3011,126 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K30" s="3">
-        <v>77</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K31" s="3">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K32" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3126,23 +3140,56 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K33" s="3">
-        <v>43</v>
+      <c r="I34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K34" s="3">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3176,6 +3223,7 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
+    <hyperlink ref="I34" r:id="rId33"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3190,178 +3238,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3381,10 +3429,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
@@ -3392,10 +3440,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -3406,7 +3454,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -3417,7 +3465,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5">
@@ -3428,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
@@ -3439,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -3450,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3471,13 +3519,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2">
@@ -3485,10 +3533,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3497,10 +3545,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3512,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18T11:06:05</t>
+    <t xml:space="preserve">2026-09-20T11:13:22</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -944,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10">
@@ -2069,7 +2069,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2104,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -2139,7 +2139,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2174,7 +2174,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2209,7 +2209,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -2244,7 +2244,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -2279,7 +2279,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2314,7 +2314,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2349,7 +2349,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2384,7 +2384,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -2419,7 +2419,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2454,7 +2454,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -2489,7 +2489,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2524,7 +2524,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -2559,7 +2559,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -2594,7 +2594,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2629,7 +2629,7 @@
         <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -2664,7 +2664,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -2699,7 +2699,7 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -2734,7 +2734,7 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2769,7 +2769,7 @@
         <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -2804,7 +2804,7 @@
         <v>161</v>
       </c>
       <c r="K23" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2839,7 +2839,7 @@
         <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -2874,7 +2874,7 @@
         <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2909,7 +2909,7 @@
         <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -2944,7 +2944,7 @@
         <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -2979,7 +2979,7 @@
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -3014,7 +3014,7 @@
         <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -3049,7 +3049,7 @@
         <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -3084,7 +3084,7 @@
         <v>202</v>
       </c>
       <c r="K31" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
@@ -3119,7 +3119,7 @@
         <v>208</v>
       </c>
       <c r="K32" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -3152,7 +3152,7 @@
         <v>213</v>
       </c>
       <c r="K33" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -3185,7 +3185,7 @@
         <v>218</v>
       </c>
       <c r="K34" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-21T12:41:34</t>
+    <t xml:space="preserve">2026-09-22T11:27:56</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
+    <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Clarivate</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-16</t>
@@ -525,184 +525,175 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -920,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -936,7 +927,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -944,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10">
@@ -1026,7 +1017,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1084,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1933,25 +1924,25 @@
         <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2004,7 +1995,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2019,22 +2010,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2057,7 +2048,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2069,7 +2060,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2083,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2104,7 +2095,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -2127,7 +2118,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2139,7 +2130,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -2162,7 +2153,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2174,7 +2165,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -2197,7 +2188,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2209,7 +2200,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -2232,7 +2223,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2244,7 +2235,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -2267,7 +2258,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2279,7 +2270,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2302,7 +2293,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2314,7 +2305,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -2337,7 +2328,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2349,7 +2340,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2372,7 +2363,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2384,7 +2375,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2407,7 +2398,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2419,7 +2410,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2442,7 +2433,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2454,7 +2445,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -2477,7 +2468,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2489,7 +2480,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -2512,7 +2503,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2524,7 +2515,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -2547,7 +2538,7 @@
         <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2559,7 +2550,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -2582,7 +2573,7 @@
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2594,7 +2585,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -2617,7 +2608,7 @@
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2629,7 +2620,7 @@
         <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2652,7 +2643,7 @@
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2664,7 +2655,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -2687,7 +2678,7 @@
         <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2699,7 +2690,7 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2722,7 +2713,7 @@
         <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2734,7 +2725,7 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2757,7 +2748,7 @@
         <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
@@ -2769,7 +2760,7 @@
         <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -2792,7 +2783,7 @@
         <v>159</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2804,7 +2795,7 @@
         <v>161</v>
       </c>
       <c r="K23" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -2827,7 +2818,7 @@
         <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2839,7 +2830,7 @@
         <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -2862,7 +2853,7 @@
         <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2874,7 +2865,7 @@
         <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2885,66 +2876,66 @@
         <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="3">
         <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K27" s="3">
-        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -2952,48 +2943,48 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="3">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
@@ -3002,7 +2993,7 @@
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3011,126 +3002,124 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="K29" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3140,56 +3129,23 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K34" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K33"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3223,7 +3179,6 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3238,178 +3193,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3429,10 +3384,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
@@ -3440,10 +3395,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -3454,7 +3409,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -3465,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -3476,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -3487,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
@@ -3498,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3519,13 +3474,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3536,7 +3491,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3545,10 +3500,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3560,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-22T11:27:56</t>
+    <t xml:space="preserve">2026-09-23T11:25:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -168,6 +168,24 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
   </si>
   <si>
@@ -186,24 +204,6 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -438,24 +438,6 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -525,6 +507,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -684,18 +678,15 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -741,16 +732,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -927,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -935,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
@@ -1017,7 +1008,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1033,7 +1024,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1191,7 +1182,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1223,7 +1214,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1252,7 +1243,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1270,7 +1261,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1284,7 +1275,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1334,7 +1325,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1371,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1590,7 +1581,7 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1595,7 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -1668,7 +1659,7 @@
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1686,7 +1677,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1735,10 +1726,10 @@
         <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>144</v>
@@ -1758,13 +1749,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1773,16 +1764,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1790,13 +1781,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1805,16 +1796,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1822,31 +1813,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -1854,31 +1845,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>12</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1886,13 +1877,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1901,16 +1892,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
@@ -1918,13 +1909,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1933,16 +1924,16 @@
         <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +1986,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2010,22 +2001,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2048,7 +2039,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2060,7 +2051,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2074,7 +2065,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2083,7 +2074,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2095,7 +2086,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2109,7 +2100,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2118,7 +2109,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2130,7 +2121,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -2141,7 +2132,7 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2153,7 +2144,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2162,10 +2153,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -2176,7 +2167,7 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2188,7 +2179,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2200,7 +2191,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -2223,7 +2214,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2232,10 +2223,10 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -2258,7 +2249,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2270,7 +2261,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -2281,7 +2272,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2293,7 +2284,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2305,7 +2296,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2328,7 +2319,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2340,7 +2331,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2354,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2375,7 +2366,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2389,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2410,7 +2401,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -2433,7 +2424,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2445,7 +2436,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2468,7 +2459,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2480,7 +2471,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -2503,7 +2494,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,10 +2503,10 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2526,7 +2517,7 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
@@ -2538,7 +2529,7 @@
         <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2550,7 +2541,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2564,7 @@
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2585,7 +2576,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -2596,7 +2587,7 @@
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2608,7 +2599,7 @@
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2617,10 +2608,10 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -2643,7 +2634,7 @@
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2655,7 +2646,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -2669,16 +2660,16 @@
         <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2690,18 +2681,18 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,33 +2701,33 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2745,103 +2736,103 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K22" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>24</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="K23" s="3">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>23</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="K24" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2850,33 +2841,33 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
@@ -2885,33 +2876,33 @@
         <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>30</v>
@@ -2920,33 +2911,33 @@
         <v>9</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -2955,30 +2946,30 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>90</v>
@@ -2990,33 +2981,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3025,33 +3016,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3060,33 +3051,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K31" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3096,30 +3087,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K32" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3129,19 +3120,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K33" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3186,185 +3177,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3384,10 +3375,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2">
@@ -3395,10 +3386,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -3409,7 +3400,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -3417,10 +3408,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
@@ -3431,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -3442,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -3453,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3474,13 +3465,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
@@ -3491,7 +3482,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3503,7 +3494,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3515,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23T11:25:20</t>
+    <t xml:space="preserve">2026-09-24T11:37:25</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -99,15 +100,15 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -279,201 +280,195 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
@@ -534,6 +529,18 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -552,18 +559,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -606,6 +601,18 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operations Engineer II</t>
   </si>
   <si>
@@ -663,30 +670,27 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -702,16 +706,22 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -720,12 +730,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
@@ -759,13 +763,13 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -910,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -926,7 +930,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10">
@@ -1008,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1024,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1032,7 +1036,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1095,7 +1099,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1182,7 +1186,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1406,10 +1410,10 @@
         <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1421,7 +1425,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1429,13 +1433,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1444,16 +1448,16 @@
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1461,31 +1465,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1493,31 +1497,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1525,31 +1529,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1557,13 +1561,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1572,13 +1576,13 @@
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>62</v>
@@ -1589,10 +1593,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1604,16 +1608,16 @@
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1621,31 +1625,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1653,31 +1657,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1691,7 +1695,7 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1700,16 +1704,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1717,13 +1721,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1732,16 +1736,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1749,13 +1753,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1764,16 +1768,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1781,31 +1785,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -1813,31 +1817,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
@@ -1845,13 +1849,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -1860,16 +1864,16 @@
         <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -1877,31 +1881,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -1909,31 +1913,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1973,7 +1977,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1986,7 +1990,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2001,22 +2005,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2039,7 +2043,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2051,7 +2055,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2065,7 +2069,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2074,7 +2078,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2086,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2109,7 +2113,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2121,7 +2125,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -2144,7 +2148,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2156,7 +2160,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2179,7 +2183,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2191,7 +2195,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2214,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2226,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -2249,7 +2253,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2261,7 +2265,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -2284,7 +2288,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2296,7 +2300,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -2310,16 +2314,16 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2328,21 +2332,21 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2351,138 +2355,138 @@
         <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
@@ -2491,30 +2495,30 @@
         <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2526,92 +2530,92 @@
         <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -2622,7 +2626,7 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2631,33 +2635,33 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2666,33 +2670,33 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2701,103 +2705,103 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K21" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K22" s="3">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="3">
         <v>23</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -2806,243 +2810,243 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K24" s="3">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="K25" s="3">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="3">
-        <v>9</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K27" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="K28" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3">
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>83</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3051,33 +3055,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3087,30 +3091,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3120,19 +3124,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3177,6 +3181,72 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3184,185 +3254,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3375,10 +3445,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3386,10 +3456,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -3400,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -3408,10 +3478,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -3419,10 +3489,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -3433,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -3444,14 +3514,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3465,13 +3535,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3482,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3494,7 +3564,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3506,7 +3576,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:37:25</t>
+    <t xml:space="preserve">2026-09-25T11:43:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -460,42 +460,27 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -541,6 +526,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -559,15 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -601,15 +586,27 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC 243952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Power Control System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">SolarEdge Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
   </si>
   <si>
@@ -742,10 +739,10 @@
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -922,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -930,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10">
@@ -1759,25 +1756,25 @@
         <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1785,31 +1782,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
@@ -1817,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1832,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24">
@@ -1849,31 +1846,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -1887,25 +1884,25 @@
         <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="3">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>10</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -1913,28 +1910,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="3">
-        <v>9</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
@@ -1990,7 +1987,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2005,22 +2002,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2043,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2055,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2078,7 +2075,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2090,7 +2087,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2113,7 +2110,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2125,7 +2122,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2148,7 +2145,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2160,7 +2157,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -2183,7 +2180,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2195,7 +2192,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -2218,7 +2215,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2230,7 +2227,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -2253,7 +2250,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2265,7 +2262,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2288,7 +2285,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2300,7 +2297,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -2323,7 +2320,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2335,7 +2332,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -2358,7 +2355,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2370,7 +2367,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2393,7 +2390,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2405,7 +2402,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -2428,7 +2425,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2440,7 +2437,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2463,7 +2460,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2475,7 +2472,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2498,7 +2495,7 @@
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2510,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2533,7 +2530,7 @@
         <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2545,7 +2542,7 @@
         <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2565,7 @@
         <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2580,7 +2577,7 @@
         <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -2603,7 +2600,7 @@
         <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2615,7 +2612,7 @@
         <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -2638,7 +2635,7 @@
         <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2650,7 +2647,7 @@
         <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -2673,7 +2670,7 @@
         <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2685,7 +2682,7 @@
         <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -2696,77 +2693,77 @@
         <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K21" s="3">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="3">
-        <v>23</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="K22" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2775,57 +2772,57 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K23" s="3">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K24" s="3">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -2836,101 +2833,101 @@
         <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>10</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="K25" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="3">
-        <v>9</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K27" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -2941,45 +2938,45 @@
         <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K28" s="3">
-        <v>9</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>4</v>
@@ -2988,10 +2985,10 @@
         <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>193</v>
@@ -3000,7 +2997,7 @@
         <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3020,33 +3017,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3055,33 +3052,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3091,30 +3088,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K32" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3124,19 +3121,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="K33" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3181,11 +3178,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3204,10 +3201,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3215,25 +3212,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3254,178 +3251,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="3">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B5" s="3">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3445,10 +3442,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3459,7 +3456,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -3470,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -3481,7 +3478,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
@@ -3492,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -3503,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -3514,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3535,13 +3532,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3552,7 +3549,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3564,7 +3561,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3576,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T11:43:55</t>
+    <t xml:space="preserve">2026-09-27T11:56:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -409,6 +409,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -424,24 +439,6 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -460,6 +457,18 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
   </si>
   <si>
@@ -487,193 +496,187 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC 243952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC 243952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
@@ -683,9 +686,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>437</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10">
@@ -1009,7 +1009,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1025,7 +1025,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1660,13 +1660,13 @@
         <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>133</v>
@@ -1692,7 +1692,7 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1701,16 +1701,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1718,13 +1718,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1733,16 +1733,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1750,31 +1750,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1782,31 +1782,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23">
@@ -1814,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1829,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
@@ -1846,13 +1846,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1861,16 +1861,16 @@
         <v>10</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -1878,13 +1878,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>28</v>
@@ -1893,13 +1893,13 @@
         <v>9</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>105</v>
@@ -1910,7 +1910,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>58</v>
@@ -1925,13 +1925,13 @@
         <v>8</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
@@ -1987,7 +1987,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2002,22 +2002,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2040,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2052,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2075,7 +2075,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2087,7 +2087,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2110,7 +2110,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2122,7 +2122,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -2145,7 +2145,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2157,7 +2157,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2180,7 +2180,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2192,7 +2192,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -2215,7 +2215,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2227,7 +2227,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -2250,7 +2250,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2262,7 +2262,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2285,7 +2285,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2297,7 +2297,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2320,7 +2320,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2332,7 +2332,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -2355,7 +2355,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2367,7 +2367,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -2390,7 +2390,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2402,7 +2402,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2425,7 +2425,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2437,7 +2437,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -2460,7 +2460,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2472,7 +2472,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2495,7 +2495,7 @@
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2507,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -2530,7 +2530,7 @@
         <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2542,7 +2542,7 @@
         <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -2565,7 +2565,7 @@
         <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2577,7 +2577,7 @@
         <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2588,19 +2588,19 @@
         <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2612,7 +2612,7 @@
         <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2623,7 +2623,7 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2632,33 +2632,33 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K19" s="3">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2667,103 +2667,103 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="K20" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>23</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K21" s="3">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>12</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K22" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2772,33 +2772,33 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="K23" s="3">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>27</v>
@@ -2807,33 +2807,33 @@
         <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>28</v>
@@ -2842,27 +2842,27 @@
         <v>9</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>58</v>
@@ -2877,33 +2877,33 @@
         <v>8</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -2912,33 +2912,33 @@
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K27" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -2947,33 +2947,33 @@
         <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="K28" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2982,33 +2982,33 @@
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>28</v>
@@ -3017,33 +3017,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3052,33 +3052,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="K31" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3088,30 +3088,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="K32" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3121,19 +3121,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="K33" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3178,11 +3178,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3201,10 +3201,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3212,25 +3212,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3251,40 +3251,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="3">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="B3" s="3">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -3295,18 +3295,18 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>224</v>
@@ -3453,7 +3453,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>245</v>
@@ -3475,7 +3475,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>247</v>
@@ -3558,7 +3558,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>254</v>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28T13:43:58</t>
+    <t xml:space="preserve">2026-09-29T12:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -351,6 +352,24 @@
     <t xml:space="preserve">2026-09-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -375,9 +394,6 @@
     <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -483,6 +499,21 @@
     <t xml:space="preserve">2026-09-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
@@ -507,6 +538,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -534,24 +583,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -687,28 +718,28 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -911,7 +942,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -919,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -927,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -935,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10">
@@ -1033,7 +1064,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1041,7 +1072,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1075,7 +1106,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1083,7 +1114,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1543,10 +1574,10 @@
         <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>115</v>
@@ -1575,10 +1606,10 @@
         <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>121</v>
@@ -1590,7 +1621,7 @@
         <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -1598,31 +1629,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1630,10 +1661,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>53</v>
@@ -1642,19 +1673,19 @@
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1662,13 +1693,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1677,16 +1708,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1700,13 +1731,13 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>138</v>
@@ -1732,25 +1763,25 @@
         <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -1758,13 +1789,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1773,16 +1804,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1790,19 +1821,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>153</v>
@@ -1822,19 +1853,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>158</v>
@@ -1846,7 +1877,7 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1854,31 +1885,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25">
@@ -1886,31 +1917,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1918,31 +1949,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +2026,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2010,22 +2041,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -2048,7 +2079,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2060,7 +2091,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2083,7 +2114,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2095,7 +2126,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2118,7 +2149,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2130,7 +2161,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2153,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2165,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -2188,7 +2219,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2200,7 +2231,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -2223,7 +2254,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2235,7 +2266,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -2258,7 +2289,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2270,7 +2301,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2293,7 +2324,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2305,7 +2336,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -2328,7 +2359,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2340,7 +2371,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2394,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2375,7 +2406,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2429,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2410,7 +2441,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -2433,7 +2464,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2445,7 +2476,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2459,16 +2490,16 @@
         <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2480,7 +2511,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2494,16 +2525,16 @@
         <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,53 +2543,53 @@
         <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="K15" s="3">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
@@ -2567,36 +2598,36 @@
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2605,22 +2636,22 @@
         <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -2631,19 +2662,19 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2655,7 +2686,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2666,42 +2697,42 @@
         <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="K20" s="3">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,45 +2741,45 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>153</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
@@ -2760,30 +2791,30 @@
         <v>155</v>
       </c>
       <c r="K22" s="3">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2792,246 +2823,246 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="K24" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="K25" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="K26" s="3">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="K28" s="3">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="K29" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>195</v>
@@ -3040,7 +3071,7 @@
         <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3051,31 +3082,31 @@
         <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K31" s="3">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -3089,7 +3120,7 @@
         <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
         <v>4</v>
@@ -3098,10 +3129,10 @@
         <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>205</v>
@@ -3110,7 +3141,7 @@
         <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
@@ -3121,50 +3152,54 @@
         <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
@@ -3176,11 +3211,77 @@
         <v>216</v>
       </c>
       <c r="K34" s="3">
-        <v>54</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K35" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="3">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3215,11 +3316,103 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3">
+        <v>41</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -3229,185 +3422,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3420,10 +3613,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -3434,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -3445,7 +3638,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -3453,10 +3646,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -3464,10 +3657,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
@@ -3478,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
@@ -3489,14 +3682,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3510,13 +3703,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2">
@@ -3524,10 +3717,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3539,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3551,7 +3744,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29T12:41:46</t>
+    <t xml:space="preserve">2026-09-30T12:27:48</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,7 +187,415 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
     <t xml:space="preserve">SAP</t>
@@ -196,262 +604,91 @@
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
@@ -460,261 +697,48 @@
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC 243952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -727,37 +751,49 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -766,22 +802,10 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -815,9 +839,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -942,7 +963,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -950,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -958,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -966,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10">
@@ -1048,7 +1069,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1106,7 +1127,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1133,7 +1154,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1251,25 +1272,25 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1277,10 +1298,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1292,16 +1313,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1315,25 +1336,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1347,25 +1368,25 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1382,22 +1403,22 @@
         <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1405,19 +1426,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1429,7 +1450,7 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1437,31 +1458,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>68</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1469,31 +1490,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1501,31 +1522,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="3">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1533,31 +1554,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1565,31 +1586,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="3">
-        <v>41</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1597,31 +1618,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -1629,31 +1650,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>44</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1661,31 +1682,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3">
+        <v>41</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>36</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1693,19 +1714,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1717,7 +1738,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -1725,31 +1746,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1763,13 +1784,13 @@
         <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>143</v>
@@ -1789,31 +1810,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1821,31 +1842,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1853,31 +1874,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1885,31 +1906,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>24</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>20</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25">
@@ -1917,31 +1938,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1949,31 +1970,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2011,7 +2032,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -2026,7 +2047,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2041,22 +2062,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2079,7 +2100,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2091,7 +2112,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2114,7 +2135,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2126,7 +2147,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2137,39 +2158,39 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K4" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2181,22 +2202,22 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K5" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2207,31 +2228,31 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K6" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2242,31 +2263,31 @@
         <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>80</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>70</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K7" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2280,51 +2301,51 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K8" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2333,313 +2354,313 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>47</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K10" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K11" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="K12" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>47</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3">
-        <v>41</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="K15" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K16" s="3">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>36</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K17" s="3">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2648,45 +2669,45 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="K18" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -2697,19 +2718,19 @@
         <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2721,74 +2742,74 @@
         <v>145</v>
       </c>
       <c r="K20" s="3">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="K21" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
         <v>41</v>
@@ -2796,293 +2817,293 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="K23" s="3">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>20</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>23</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>12</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K25" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="K26" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K28" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="K29" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="K30" s="3">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3091,33 +3112,33 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3126,33 +3147,33 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>28</v>
@@ -3161,33 +3182,33 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K33" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3196,33 +3217,33 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K34" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3232,56 +3253,89 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K35" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
         <v>0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K36" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K36" s="3">
-        <v>55</v>
+      <c r="I37" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K37" s="3">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K37"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3318,6 +3372,7 @@
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
     <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3325,8 +3380,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3348,10 +3403,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3359,55 +3414,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>74</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3415,185 +3542,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3613,10 +3740,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -3624,10 +3751,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
@@ -3638,7 +3765,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
@@ -3649,7 +3776,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
@@ -3660,7 +3787,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
@@ -3671,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -3682,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3703,13 +3830,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2">
@@ -3720,7 +3847,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3729,10 +3856,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3744,7 +3871,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30T12:27:48</t>
+    <t xml:space="preserve">2026-10-01T13:03:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,6 +187,24 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -199,39 +217,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -310,21 +313,6 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -337,24 +325,6 @@
     <t xml:space="preserve">2026-08-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -373,126 +343,114 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -535,6 +493,45 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -553,42 +550,12 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">COM-C-TECH LTD</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory, Windows Server</t>
   </si>
   <si>
@@ -598,12 +565,6 @@
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any), Automation</t>
   </si>
   <si>
@@ -643,7 +604,7 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Power Control System Engineer</t>
@@ -691,154 +652,142 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -963,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -971,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -979,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -987,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1018,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1077,7 +1026,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1085,7 +1034,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1127,7 +1076,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1154,7 +1103,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1272,25 +1221,25 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1298,10 +1247,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1313,16 +1262,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1354,7 +1303,7 @@
         <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1362,10 +1311,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>53</v>
@@ -1377,16 +1326,16 @@
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1394,13 +1343,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1409,16 +1358,16 @@
         <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1426,13 +1375,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1441,16 +1390,16 @@
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1458,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1473,16 +1422,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1490,10 +1439,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>53</v>
@@ -1505,16 +1454,16 @@
         <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1522,31 +1471,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1557,28 +1506,28 @@
         <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1586,31 +1535,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1618,31 +1567,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -1650,31 +1599,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1688,25 +1637,25 @@
         <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>36</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3">
-        <v>41</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -1714,31 +1663,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1746,31 +1695,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>39</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1778,31 +1727,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1810,31 +1759,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1842,31 +1791,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1880,25 +1829,25 @@
         <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
@@ -1906,31 +1855,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -1944,13 +1893,13 @@
         <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>165</v>
@@ -1962,7 +1911,7 @@
         <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
@@ -1970,31 +1919,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +1981,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -2047,7 +1996,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2062,22 +2011,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2100,7 +2049,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2112,7 +2061,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2135,7 +2084,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2147,7 +2096,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2158,39 +2107,39 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2202,22 +2151,22 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2189,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2249,18 +2198,18 @@
         <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>53</v>
@@ -2272,33 +2221,33 @@
         <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2307,33 +2256,33 @@
         <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2342,33 +2291,33 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2377,30 +2326,30 @@
         <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>53</v>
@@ -2412,57 +2361,57 @@
         <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2470,139 +2419,139 @@
         <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -2613,206 +2562,206 @@
         <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>36</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="3">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>39</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K19" s="3">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="K20" s="3">
-        <v>79</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="K21" s="3">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K22" s="3">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -2823,66 +2772,66 @@
         <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="K23" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="K24" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2893,19 +2842,19 @@
         <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2914,428 +2863,325 @@
         <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="K25" s="3">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="K26" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="3">
-        <v>10</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K29" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K30" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>8</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K33" s="3">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K34" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K35" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K36" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="K37" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3370,9 +3216,6 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3380,11 +3223,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3403,10 +3246,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3414,127 +3257,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>84</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>74</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>52</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3542,185 +3289,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3740,10 +3487,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
@@ -3751,10 +3498,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -3762,10 +3509,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -3773,10 +3520,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -3787,7 +3534,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -3798,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
@@ -3809,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3830,13 +3577,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3847,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3856,10 +3603,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3871,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -5,16 +5,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
-    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
-    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
-    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
+    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
+    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01T13:03:03</t>
+    <t xml:space="preserve">2026-10-02T12:24:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -493,6 +492,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -517,6 +531,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -532,36 +564,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -676,13 +678,13 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
@@ -920,7 +922,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +1036,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1042,7 +1044,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1861,13 +1863,13 @@
         <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
@@ -1879,7 +1881,7 @@
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -1887,13 +1889,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1902,16 +1904,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -1919,31 +1921,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2061,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2096,7 +2098,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2131,7 +2133,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -2166,7 +2168,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -2201,7 +2203,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2236,7 +2238,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -2271,7 +2273,7 @@
         <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2306,7 +2308,7 @@
         <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -2341,7 +2343,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -2376,7 +2378,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -2411,7 +2413,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -2446,7 +2448,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2481,7 +2483,7 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2516,7 +2518,7 @@
         <v>120</v>
       </c>
       <c r="K15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2551,7 +2553,7 @@
         <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -2586,7 +2588,7 @@
         <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -2621,7 +2623,7 @@
         <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -2656,7 +2658,7 @@
         <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2691,7 +2693,7 @@
         <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2726,7 +2728,7 @@
         <v>148</v>
       </c>
       <c r="K21" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -2761,7 +2763,7 @@
         <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -2796,7 +2798,7 @@
         <v>114</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2807,13 +2809,13 @@
         <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
@@ -2828,21 +2830,21 @@
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2851,7 +2853,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>177</v>
@@ -2860,48 +2862,48 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="K26" s="3">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -2912,36 +2914,36 @@
         <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>58</v>
@@ -2956,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>177</v>
@@ -2965,24 +2967,24 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2991,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>177</v>
@@ -3000,24 +3002,24 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3026,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>177</v>
@@ -3035,21 +3037,21 @@
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>141</v>
@@ -3061,7 +3063,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>177</v>
@@ -3070,24 +3072,24 @@
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3096,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>177</v>
@@ -3105,24 +3107,24 @@
         <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K32" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3138,24 +3140,24 @@
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K33" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3171,13 +3173,13 @@
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K34" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3223,72 +3225,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="3">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G2"/>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-  </hyperlinks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3296,21 +3232,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>221</v>
@@ -3318,163 +3254,163 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3487,10 +3423,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
@@ -3501,7 +3437,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -3512,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -3520,10 +3456,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -3531,10 +3467,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -3545,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
@@ -3556,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3577,13 +3513,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -3594,7 +3530,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3606,7 +3542,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3618,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02T12:24:05</t>
+    <t xml:space="preserve">2026-10-04T12:16:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -360,24 +361,6 @@
     <t xml:space="preserve">2026-09-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -492,15 +475,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
   </si>
   <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
   </si>
   <si>
@@ -519,199 +508,202 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dundee, Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4978622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -922,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -930,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -938,7 +930,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -1020,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1036,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1044,7 +1036,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1575,25 +1567,25 @@
         <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>39</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1601,31 +1593,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>36</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1633,10 +1625,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>53</v>
@@ -1645,19 +1637,19 @@
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1665,31 +1657,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1706,10 +1698,10 @@
         <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>136</v>
@@ -1729,13 +1721,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1744,16 +1736,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -1761,31 +1753,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1793,31 +1785,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
@@ -1825,13 +1817,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1840,16 +1832,16 @@
         <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
@@ -1857,10 +1849,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>111</v>
@@ -1872,16 +1864,16 @@
         <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -1889,10 +1881,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>105</v>
@@ -1904,13 +1896,13 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>72</v>
@@ -1921,31 +1913,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +1990,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2013,22 +2005,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
@@ -2051,7 +2043,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2063,7 +2055,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2086,7 +2078,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2098,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2121,7 +2113,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2133,7 +2125,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2156,7 +2148,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2168,7 +2160,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -2191,7 +2183,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2203,7 +2195,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2226,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2238,7 +2230,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -2261,7 +2253,7 @@
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2273,7 +2265,7 @@
         <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2296,7 +2288,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2308,7 +2300,7 @@
         <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -2331,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
@@ -2343,7 +2335,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -2366,7 +2358,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2378,7 +2370,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -2401,7 +2393,7 @@
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2413,7 +2405,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2436,7 +2428,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2448,7 +2440,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2471,7 +2463,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2483,7 +2475,7 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2494,74 +2486,74 @@
         <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>36</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K16" s="3">
-        <v>43</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
@@ -2570,60 +2562,60 @@
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="3">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -2637,16 +2629,16 @@
         <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2658,18 +2650,18 @@
         <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2678,103 +2670,103 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K20" s="3">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K21" s="3">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="K22" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
@@ -2783,30 +2775,30 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K23" s="3">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>111</v>
@@ -2818,30 +2810,30 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K24" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>105</v>
@@ -2853,89 +2845,89 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K26" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="K27" s="3">
         <v>39</v>
@@ -2943,7 +2935,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>58</v>
@@ -2958,33 +2950,33 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2993,33 +2985,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K29" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3028,33 +3020,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>28</v>
@@ -3063,33 +3055,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3098,33 +3090,33 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K32" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3134,30 +3126,30 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K33" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3167,19 +3159,19 @@
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K34" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3225,6 +3217,72 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="41" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3232,185 +3290,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3423,10 +3481,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3434,10 +3492,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -3448,7 +3506,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -3456,10 +3514,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -3467,10 +3525,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -3481,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -3492,14 +3550,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3513,13 +3571,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3530,7 +3588,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3542,7 +3600,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3554,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T14:26:43</t>
+    <t xml:space="preserve">2026-10-06T13:14:31</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,6 +217,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -250,9 +265,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -346,19 +358,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Terraform/IaC, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-stealth-startup-4473602938</t>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
@@ -499,6 +529,24 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -514,9 +562,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (37577)</t>
   </si>
   <si>
@@ -529,22 +574,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
+    <t xml:space="preserve">Network Operations &amp; Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
@@ -610,7 +649,7 @@
     <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Israel</t>
@@ -715,154 +754,145 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -995,7 +1025,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1011,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1093,7 +1123,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1109,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1151,7 +1181,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1179,7 +1209,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1360,25 +1390,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1386,31 +1416,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>84</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1418,19 +1448,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1442,7 +1472,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1450,31 +1480,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>74</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -1482,31 +1512,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -1514,31 +1544,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>68</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1546,31 +1576,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3">
-        <v>61</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1578,31 +1608,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>60</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -1610,31 +1640,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1642,31 +1672,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1683,10 +1713,10 @@
         <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>122</v>
@@ -1706,31 +1736,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -1744,25 +1774,25 @@
         <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1770,31 +1800,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -1808,13 +1838,13 @@
         <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>141</v>
@@ -1826,7 +1856,7 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1840,25 +1870,25 @@
         <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1866,28 +1896,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
@@ -1898,31 +1928,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -1930,31 +1960,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1971,10 +2001,10 @@
         <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>164</v>
@@ -1986,7 +2016,7 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
@@ -1994,31 +2024,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2057,7 +2087,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2136,7 +2166,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2171,7 +2201,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2236,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -2241,7 +2271,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -2252,16 +2282,16 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>88</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>176</v>
@@ -2270,33 +2300,33 @@
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>84</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>176</v>
@@ -2305,30 +2335,30 @@
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
@@ -2343,30 +2373,30 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>80</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>74</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>176</v>
@@ -2375,33 +2405,33 @@
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>176</v>
@@ -2410,103 +2440,103 @@
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K10" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>68</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3">
-        <v>61</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>176</v>
@@ -2515,33 +2545,33 @@
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>176</v>
@@ -2550,33 +2580,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>176</v>
@@ -2585,13 +2615,13 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="K15" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2605,10 +2635,10 @@
         <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>122</v>
@@ -2626,27 +2656,27 @@
         <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3">
+        <v>47</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>176</v>
@@ -2655,13 +2685,13 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2672,16 +2702,16 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>176</v>
@@ -2690,33 +2720,33 @@
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>176</v>
@@ -2725,13 +2755,13 @@
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2742,13 +2772,13 @@
         <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>141</v>
@@ -2763,10 +2793,10 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K20" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2777,16 +2807,16 @@
         <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E21" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>176</v>
@@ -2795,33 +2825,33 @@
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K21" s="3">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>176</v>
@@ -2830,33 +2860,33 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>176</v>
@@ -2865,33 +2895,33 @@
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>176</v>
@@ -2900,13 +2930,13 @@
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -2920,10 +2950,10 @@
         <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>164</v>
@@ -2938,30 +2968,30 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>176</v>
@@ -2970,24 +3000,24 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -2996,7 +3026,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>176</v>
@@ -3005,33 +3035,33 @@
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="K27" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>176</v>
@@ -3040,13 +3070,13 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="K28" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3057,51 +3087,51 @@
         <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>24</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="3">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>176</v>
@@ -3110,33 +3140,33 @@
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="3">
+        <v>23</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>176</v>
@@ -3145,13 +3175,13 @@
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K31" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -3162,66 +3192,66 @@
         <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="K32" s="3">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -3229,19 +3259,19 @@
         <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>176</v>
@@ -3250,33 +3280,33 @@
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="K34" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>176</v>
@@ -3285,13 +3315,13 @@
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -3305,13 +3335,13 @@
         <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>176</v>
@@ -3320,133 +3350,139 @@
         <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="K36" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>8</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="K37" s="3">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>230</v>
+        <v>163</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K38" s="3">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
+      <c r="J39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="K39" s="3">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>176</v>
       </c>
@@ -3454,17 +3490,83 @@
         <v>34</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K40" s="3">
-        <v>61</v>
+      <c r="B41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K41" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K42" s="3">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K40"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3505,6 +3607,8 @@
     <hyperlink ref="I38" r:id="rId37"/>
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3512,11 +3616,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3546,175 +3650,55 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3">
-        <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3729,178 +3713,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B9" s="3">
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3920,10 +3904,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -3931,10 +3915,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -3945,7 +3929,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -3953,10 +3937,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
@@ -3967,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -3978,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -3989,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4010,13 +3994,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2">
@@ -4027,7 +4011,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4036,10 +4020,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4051,7 +4035,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-06T13:14:31</t>
+    <t xml:space="preserve">2026-10-07T13:12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,12 +103,12 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -217,54 +217,42 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -310,6 +298,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -358,276 +358,264 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4475569150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations &amp; Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-malamteam-4476555528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
@@ -640,6 +628,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -670,13 +667,13 @@
     <t xml:space="preserve">Optimove</t>
   </si>
   <si>
-    <t xml:space="preserve">Dundee, Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4978622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
@@ -790,6 +787,9 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -799,9 +799,6 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -817,36 +814,36 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
@@ -877,10 +874,10 @@
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1025,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1033,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1041,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1123,7 +1120,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1131,7 +1128,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1139,7 +1136,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1155,7 +1152,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1181,7 +1178,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -1189,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1209,7 +1206,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1297,7 +1294,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1390,25 +1387,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1416,31 +1413,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1448,19 +1445,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1472,7 +1469,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1480,31 +1477,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -1512,31 +1509,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1544,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1559,16 +1556,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1664,7 +1661,7 @@
         <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1684,7 +1681,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>117</v>
@@ -1696,7 +1693,7 @@
         <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -1707,28 +1704,28 @@
         <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>48</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1736,19 +1733,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
@@ -1774,25 +1771,25 @@
         <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -1800,31 +1797,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3">
+        <v>39</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1832,31 +1829,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1870,22 @@
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -1896,28 +1893,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>28</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>39</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
@@ -1928,31 +1925,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>36</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -1960,19 +1957,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>159</v>
@@ -1984,7 +1981,7 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
@@ -1992,31 +1989,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -2024,31 +2021,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2084,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2101,7 +2098,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2116,22 +2113,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2154,7 +2151,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2166,7 +2163,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2180,7 +2177,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2189,7 +2186,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2201,7 +2198,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2224,7 +2221,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2236,7 +2233,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -2259,7 +2256,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2271,7 +2268,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -2282,89 +2279,89 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2373,91 +2370,91 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K9" s="3">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2466,22 +2463,22 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K11" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2504,7 +2501,7 @@
         <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>33</v>
@@ -2516,7 +2513,7 @@
         <v>103</v>
       </c>
       <c r="K12" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -2539,7 +2536,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2551,7 +2548,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2574,7 +2571,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2583,10 +2580,10 @@
         <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2603,13 +2600,13 @@
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2618,10 +2615,10 @@
         <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2629,57 +2626,57 @@
         <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>48</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K16" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2691,7 +2688,7 @@
         <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -2702,101 +2699,101 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="K18" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K20" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -2810,121 +2807,121 @@
         <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="K21" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>39</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>36</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="K23" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2933,91 +2930,91 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="K24" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="K25" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="K26" s="3">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3026,33 +3023,33 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K27" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3061,33 +3058,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3096,45 +3093,45 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
@@ -3146,7 +3143,7 @@
         <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -3157,42 +3154,42 @@
         <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K31" s="3">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
@@ -3204,19 +3201,19 @@
         <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
@@ -3224,10 +3221,10 @@
         <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3236,33 +3233,33 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K33" s="3">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3271,33 +3268,33 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3306,33 +3303,33 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="K35" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3341,27 +3338,27 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="K36" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>58</v>
@@ -3376,33 +3373,33 @@
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K37" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3411,33 +3408,33 @@
         <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="K38" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -3446,33 +3443,33 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3481,33 +3478,33 @@
         <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="K40" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -3517,30 +3514,30 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="K41" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
@@ -3550,19 +3547,19 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="K42" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3616,11 +3613,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3639,10 +3636,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3650,55 +3647,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>189</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3713,178 +3758,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="3">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="B3" s="3">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="3">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B8" s="3">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B9" s="3">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B13" s="3">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B13" s="3">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="3">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B14" s="3">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="3">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="B15" s="3">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" s="3">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B16" s="3">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3904,10 +3949,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -3915,10 +3960,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3">
@@ -3926,10 +3971,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -3937,10 +3982,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">
@@ -3951,7 +3996,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
@@ -3959,10 +4004,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
@@ -3973,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3994,13 +4039,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="2">
@@ -4008,10 +4053,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4020,10 +4065,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4035,7 +4080,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-07T13:12:55</t>
+    <t xml:space="preserve">2026-10-08T13:19:24</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -253,6 +253,24 @@
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -271,12 +289,6 @@
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
   </si>
   <si>
@@ -358,6 +370,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -373,18 +400,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -403,6 +418,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineer Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -502,6 +532,24 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -529,25 +577,7 @@
     <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477158844</t>
   </si>
   <si>
     <t xml:space="preserve">Network Operations &amp; Control</t>
@@ -562,15 +592,6 @@
     <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-malamteam-4476555528</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -628,15 +649,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -661,21 +673,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -781,13 +778,22 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
@@ -797,15 +803,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
@@ -1014,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1030,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1038,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1128,7 +1125,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1136,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1144,7 +1141,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1175,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1206,7 +1203,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1451,25 +1448,25 @@
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1477,19 +1474,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>87</v>
@@ -1501,7 +1498,7 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1509,31 +1506,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -1541,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1556,16 +1553,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1576,28 +1573,28 @@
         <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>68</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1605,31 +1602,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>68</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="3">
-        <v>61</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1637,31 +1634,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>61</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>60</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1669,31 +1666,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1701,31 +1698,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1742,10 +1739,10 @@
         <v>125</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
@@ -1757,7 +1754,7 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
@@ -1765,19 +1762,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>131</v>
@@ -1789,7 +1786,7 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1797,31 +1794,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1829,31 +1826,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -1870,22 +1867,22 @@
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1893,10 +1890,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>53</v>
@@ -1905,19 +1902,19 @@
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -1925,31 +1922,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -1957,19 +1954,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>159</v>
@@ -1981,7 +1978,7 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1989,31 +1986,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="3">
+        <v>27</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>24</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2021,31 +2018,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2163,7 +2160,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2198,7 +2195,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2233,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -2268,7 +2265,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2300,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2338,7 +2335,7 @@
         <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2349,16 +2346,16 @@
         <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>177</v>
@@ -2367,30 +2364,30 @@
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>87</v>
@@ -2405,30 +2402,30 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>177</v>
@@ -2437,24 +2434,24 @@
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K10" s="3">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2463,7 +2460,7 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>177</v>
@@ -2472,13 +2469,13 @@
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2486,89 +2483,89 @@
         <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>68</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>68</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="3">
-        <v>61</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="K13" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>177</v>
@@ -2577,33 +2574,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>177</v>
@@ -2612,33 +2609,33 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>177</v>
@@ -2647,13 +2644,13 @@
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="K16" s="3">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2667,10 +2664,10 @@
         <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
@@ -2685,27 +2682,27 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="K17" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>131</v>
@@ -2720,65 +2717,65 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>177</v>
@@ -2787,13 +2784,13 @@
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="K20" s="3">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2807,10 +2804,10 @@
         <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
@@ -2819,24 +2816,24 @@
         <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>53</v>
@@ -2845,10 +2842,10 @@
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>177</v>
@@ -2857,65 +2854,65 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>159</v>
@@ -2930,30 +2927,30 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>24</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>177</v>
@@ -2962,33 +2959,33 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>177</v>
@@ -2997,13 +2994,13 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K26" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -3014,7 +3011,7 @@
         <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3023,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>177</v>
@@ -3032,24 +3029,24 @@
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3058,7 +3055,7 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>177</v>
@@ -3067,10 +3064,10 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3078,10 +3075,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>125</v>
@@ -3093,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>177</v>
@@ -3102,33 +3099,33 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>177</v>
@@ -3137,59 +3134,59 @@
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
@@ -3198,33 +3195,33 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3233,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>177</v>
@@ -3242,24 +3239,24 @@
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="K33" s="3">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3268,7 +3265,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>177</v>
@@ -3277,24 +3274,24 @@
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3303,7 +3300,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>177</v>
@@ -3312,68 +3309,68 @@
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K35" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>59</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="K36" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>177</v>
@@ -3382,129 +3379,127 @@
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K40" s="3">
-        <v>27</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -3517,53 +3512,20 @@
         <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K41" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K42" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K41"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3605,7 +3567,6 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3613,9 +3574,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3647,79 +3608,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -3728,13 +3689,13 @@
         <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3758,178 +3719,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="3">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="B2" s="3">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="3">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="B6" s="3">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="3">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="B9" s="3">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="B11" s="3">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B12" s="3">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="3">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B13" s="3">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="B15" s="3">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3949,10 +3910,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2">
@@ -3960,10 +3921,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -3971,10 +3932,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -3982,10 +3943,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -3993,10 +3954,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -4007,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -4018,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4039,13 +4000,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2">
@@ -4053,10 +4014,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4068,7 +4029,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4080,7 +4041,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-08T13:19:24</t>
+    <t xml:space="preserve">2026-10-09T13:07:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,6 +217,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -250,9 +265,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -298,7 +310,7 @@
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+    <t xml:space="preserve">Amazon</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
@@ -307,7 +319,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
@@ -385,6 +397,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -418,21 +448,6 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -514,7 +529,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">Fetcherr</t>
@@ -532,33 +562,12 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -649,6 +658,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -778,15 +796,15 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -823,22 +841,22 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
@@ -1011,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1133,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1175,7 +1193,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1183,7 +1201,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1384,25 +1402,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1410,31 +1428,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>84</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1442,31 +1460,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>84</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>83</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1474,31 +1492,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>80</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1506,19 +1524,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
         <v>80</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3">
-        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1530,7 +1548,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1538,31 +1556,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -1570,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1585,16 +1603,16 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -1605,28 +1623,28 @@
         <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>68</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1634,31 +1652,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>68</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>61</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1666,31 +1684,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="3">
+        <v>61</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>60</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1698,31 +1716,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>60</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3">
-        <v>57</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -1730,31 +1748,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3">
+        <v>57</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>48</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1762,31 +1780,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>54</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1794,31 +1812,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
@@ -1826,19 +1844,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>141</v>
@@ -1850,7 +1868,7 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1858,19 +1876,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
@@ -1882,7 +1900,7 @@
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -1896,25 +1914,25 @@
         <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -1928,25 +1946,25 @@
         <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>36</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <v>34</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -1954,31 +1972,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1986,19 +2004,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>164</v>
@@ -2010,7 +2028,7 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
@@ -2027,7 +2045,7 @@
         <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3">
         <v>27</v>
@@ -2042,7 +2060,7 @@
         <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2113,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2110,22 +2128,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2148,7 +2166,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2160,7 +2178,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2201,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2195,7 +2213,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2218,7 +2236,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2230,7 +2248,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2253,7 +2271,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2265,7 +2283,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -2276,159 +2294,159 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>88</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>84</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>84</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>83</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>83</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>80</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
         <v>80</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3">
-        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2437,56 +2455,56 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K11" s="3">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2495,22 +2513,22 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -2518,171 +2536,171 @@
         <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>70</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K13" s="3">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="K14" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3">
+        <v>61</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K15" s="3">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="3">
-        <v>57</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3">
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K17" s="3">
         <v>1</v>
@@ -2690,95 +2708,95 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>54</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="K18" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>48</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2787,33 +2805,33 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2822,10 +2840,10 @@
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K21" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2836,31 +2854,31 @@
         <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -2871,89 +2889,89 @@
         <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>36</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="3">
-        <v>34</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K24" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2962,10 +2980,10 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="K25" s="3">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -2979,7 +2997,7 @@
         <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3">
         <v>27</v>
@@ -2988,7 +3006,7 @@
         <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
@@ -2997,56 +3015,56 @@
         <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="K26" s="3">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>27</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>24</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3055,33 +3073,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3090,10 +3108,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3102,21 +3120,21 @@
         <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="K29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3125,103 +3143,103 @@
         <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="K30" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>24</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="3">
-        <v>23</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K31" s="3">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K32" s="3">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3230,302 +3248,372 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K33" s="3">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K34" s="3">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K35" s="3">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="K36" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="K37" s="3">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>58</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>143</v>
       </c>
       <c r="K38" s="3">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K39" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="K40" s="3">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K41" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K41" s="3">
-        <v>64</v>
+      <c r="J42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K42" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K43" s="3">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K43"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3567,6 +3655,8 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3574,9 +3664,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3597,10 +3687,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3608,103 +3698,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3">
-        <v>57</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3719,178 +3737,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3910,10 +3928,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -3921,10 +3939,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -3932,10 +3950,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -3943,10 +3961,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -3957,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -3968,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -3979,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4000,13 +4018,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2">
@@ -4014,10 +4032,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4026,10 +4044,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4041,7 +4059,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T13:07:23</t>
+    <t xml:space="preserve">2026-10-11T12:40:01</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,54 +217,60 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -367,21 +373,6 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -529,6 +520,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -547,21 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -658,15 +649,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -817,18 +799,18 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
@@ -841,6 +823,12 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -851,12 +839,6 @@
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
@@ -1029,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1053,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -1135,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1151,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1193,7 +1175,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -1402,25 +1384,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1428,13 +1410,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>28</v>
@@ -1443,16 +1425,16 @@
         <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1460,13 +1442,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1475,16 +1457,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1474,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1507,16 +1489,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -1524,10 +1506,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>53</v>
@@ -1539,16 +1521,16 @@
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1556,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1571,16 +1553,16 @@
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -1588,13 +1570,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1603,13 +1585,13 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>62</v>
@@ -1620,7 +1602,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>58</v>
@@ -1635,16 +1617,16 @@
         <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1652,13 +1634,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -1667,16 +1649,16 @@
         <v>68</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1684,10 +1666,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>53</v>
@@ -1699,16 +1681,16 @@
         <v>61</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1716,31 +1698,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1748,31 +1730,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1780,31 +1762,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
@@ -1812,31 +1794,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1844,31 +1826,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -1876,31 +1858,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1908,31 +1890,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1940,31 +1922,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -1972,31 +1954,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -2004,31 +1986,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
@@ -2036,31 +2018,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
         <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2095,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2128,22 +2110,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2166,7 +2148,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2178,7 +2160,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2201,7 +2183,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2213,7 +2195,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2236,7 +2218,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2248,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -2271,7 +2253,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2283,7 +2265,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -2294,42 +2276,42 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
@@ -2338,33 +2320,33 @@
         <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2373,33 +2355,33 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2408,30 +2390,30 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
@@ -2443,33 +2425,33 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2478,33 +2460,33 @@
         <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2513,27 +2495,27 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K12" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>58</v>
@@ -2548,33 +2530,33 @@
         <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
@@ -2583,30 +2565,30 @@
         <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>53</v>
@@ -2618,453 +2600,453 @@
         <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="K20" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K21" s="3">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="K22" s="3">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="K23" s="3">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E25" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K25" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
         <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>24</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K27" s="3">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3073,33 +3055,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>90</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3108,10 +3090,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3120,21 +3102,21 @@
         <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3143,103 +3125,103 @@
         <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3248,372 +3230,302 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="K33" s="3">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="K35" s="3">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>12</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="K36" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>236</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K41" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K42" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="K43" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K41"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3655,8 +3567,6 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3664,9 +3574,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3687,10 +3597,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3698,25 +3608,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3737,178 +3647,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3838,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3939,10 +3849,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -3953,7 +3863,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -3961,10 +3871,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -3975,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -3986,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -3997,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4018,13 +3928,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -4035,7 +3945,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4044,10 +3954,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4059,7 +3969,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -25,13 +25,13 @@
     <t xml:space="preserve">Week</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-W41</t>
+    <t xml:space="preserve">2026-W42</t>
   </si>
   <si>
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T12:40:01</t>
+    <t xml:space="preserve">2026-10-12T15:13:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -328,264 +328,264 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4476025268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4478393138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations &amp; Control</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
   </si>
   <si>
@@ -691,10 +691,7 @@
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4475685553</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -772,21 +769,30 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -796,15 +802,6 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
@@ -823,22 +820,22 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
@@ -1019,7 +1016,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1027,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1035,7 +1032,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1114,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1122,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1605,28 +1602,28 @@
         <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -1634,31 +1631,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1666,31 +1663,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -1698,31 +1695,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
@@ -1730,31 +1727,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -1762,31 +1759,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -1794,19 +1791,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>138</v>
@@ -1826,19 +1823,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>143</v>
@@ -1850,7 +1847,7 @@
         <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -1914,7 +1911,7 @@
         <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
@@ -1922,13 +1919,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1937,16 +1934,16 @@
         <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -2018,7 +2015,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>168</v>
@@ -2160,7 +2157,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2195,7 +2192,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -2230,7 +2227,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -2265,7 +2262,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -2300,7 +2297,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2335,7 +2332,7 @@
         <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2370,7 +2367,7 @@
         <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2405,7 +2402,7 @@
         <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2440,7 +2437,7 @@
         <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -2475,7 +2472,7 @@
         <v>84</v>
       </c>
       <c r="K11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2510,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="K12" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -2518,89 +2515,89 @@
         <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K13" s="3">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>178</v>
@@ -2609,33 +2606,33 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="K15" s="3">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>178</v>
@@ -2644,10 +2641,10 @@
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K16" s="3">
         <v>3</v>
@@ -2655,22 +2652,22 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>178</v>
@@ -2679,33 +2676,33 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>178</v>
@@ -2714,30 +2711,30 @@
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="K18" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>138</v>
@@ -2755,24 +2752,24 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>143</v>
@@ -2787,10 +2784,10 @@
         <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2825,7 +2822,7 @@
         <v>62</v>
       </c>
       <c r="K21" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -2857,21 +2854,21 @@
         <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="K22" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
@@ -2880,7 +2877,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>178</v>
@@ -2889,13 +2886,13 @@
         <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2930,7 +2927,7 @@
         <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -2965,12 +2962,12 @@
         <v>78</v>
       </c>
       <c r="K25" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>168</v>
@@ -3000,7 +2997,7 @@
         <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -3011,7 +3008,7 @@
         <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3035,7 +3032,7 @@
         <v>183</v>
       </c>
       <c r="K27" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -3046,7 +3043,7 @@
         <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3067,10 +3064,10 @@
         <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="K28" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3078,10 +3075,10 @@
         <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3105,7 +3102,7 @@
         <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -3116,7 +3113,7 @@
         <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3140,7 +3137,7 @@
         <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -3175,7 +3172,7 @@
         <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -3210,7 +3207,7 @@
         <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -3245,7 +3242,7 @@
         <v>172</v>
       </c>
       <c r="K33" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -3256,7 +3253,7 @@
         <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3280,7 +3277,7 @@
         <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3315,7 +3312,7 @@
         <v>172</v>
       </c>
       <c r="K35" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36">
@@ -3347,10 +3344,10 @@
         <v>221</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K36" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -3382,21 +3379,21 @@
         <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="K37" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
@@ -3405,7 +3402,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>178</v>
@@ -3414,24 +3411,24 @@
         <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="K38" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3440,7 +3437,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>178</v>
@@ -3449,24 +3446,24 @@
         <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="K39" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
@@ -3482,24 +3479,24 @@
         <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="K40" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -3515,13 +3512,13 @@
         <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="K41" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3574,8 +3571,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3608,31 +3605,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3647,178 +3740,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3">
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="3">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="B6" s="3">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" s="3">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B8" s="3">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="3">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" s="3">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B10" s="3">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B11" s="3">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B12" s="3">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3838,10 +3931,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3849,10 +3942,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -3860,10 +3953,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -3874,7 +3967,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -3885,7 +3978,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
@@ -3896,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
@@ -3907,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3928,13 +4021,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -3945,7 +4038,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3954,10 +4047,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3969,7 +4062,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-12T15:13:30</t>
+    <t xml:space="preserve">2026-10-13T14:04:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -151,6 +151,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
@@ -169,580 +187,592 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4478769750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPD Hosting LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
   </si>
   <si>
     <t xml:space="preserve">F5</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
   </si>
   <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4476025268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4478393138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4475685553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-sela-4476440697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
     <t xml:space="preserve">Student Success Coach</t>
@@ -769,6 +799,9 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
@@ -781,27 +814,24 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
@@ -820,36 +850,36 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -881,9 +911,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1016,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1024,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1114,7 +1141,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1122,7 +1149,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1130,7 +1157,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1172,7 +1199,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1180,7 +1207,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1199,9 +1226,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1256,7 +1283,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1265,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>49</v>
@@ -1288,7 +1315,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1320,7 +1347,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1349,25 +1376,25 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1375,31 +1402,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1407,31 +1434,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1439,13 +1466,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1454,16 +1481,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1471,13 +1498,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1486,16 +1513,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -1503,13 +1530,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1518,16 +1545,16 @@
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -1535,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1550,16 +1577,16 @@
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -1567,13 +1594,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1582,16 +1609,16 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1599,13 +1626,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1614,16 +1641,16 @@
         <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1631,13 +1658,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1646,16 +1673,16 @@
         <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1663,13 +1690,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>28</v>
@@ -1678,16 +1705,16 @@
         <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -1695,13 +1722,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1710,16 +1737,16 @@
         <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1727,31 +1754,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1759,31 +1786,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -1791,31 +1818,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1823,31 +1850,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1855,31 +1882,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -1887,31 +1914,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -1919,31 +1946,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3">
         <v>27</v>
       </c>
-      <c r="F23" s="3">
-        <v>34</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -1951,31 +1978,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25">
@@ -1983,31 +2010,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26">
@@ -2015,31 +2042,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2077,9 +2104,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2092,7 +2119,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2107,22 +2134,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2">
@@ -2136,7 +2163,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2145,10 +2172,10 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>49</v>
@@ -2157,7 +2184,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2171,7 +2198,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2180,7 +2207,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2192,7 +2219,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2233,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2215,7 +2242,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2227,7 +2254,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -2238,112 +2265,112 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K5" s="3">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2352,33 +2379,33 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2387,33 +2414,33 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2422,33 +2449,33 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2457,33 +2484,33 @@
         <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2492,33 +2519,33 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2527,33 +2554,33 @@
         <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
@@ -2562,33 +2589,33 @@
         <v>61</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>28</v>
@@ -2597,33 +2624,33 @@
         <v>57</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>27</v>
@@ -2632,159 +2659,159 @@
         <v>54</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -2792,223 +2819,223 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K21" s="3">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3">
         <v>27</v>
       </c>
-      <c r="E23" s="3">
-        <v>34</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="K24" s="3">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="K25" s="3">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K26" s="3">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3017,512 +3044,603 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K27" s="3">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="K30" s="3">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K31" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="K32" s="3">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>101</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="K33" s="3">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K34" s="3">
         <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K34" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="K35" s="3">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="K36" s="3">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>8</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>228</v>
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>229</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="K38" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="K39" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="K40" s="3">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K41" s="3">
-        <v>68</v>
+      <c r="I44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K44" s="3">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K44"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3564,6 +3682,9 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3572,8 +3693,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3594,10 +3715,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3605,127 +3726,169 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3740,178 +3903,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3931,10 +4094,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -3942,10 +4105,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -3953,10 +4116,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
@@ -3964,10 +4127,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
@@ -3978,7 +4141,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -3989,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
@@ -4000,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4021,13 +4184,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
@@ -4035,10 +4198,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4047,10 +4210,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4062,7 +4225,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-14T11:42:37</t>
+    <t xml:space="preserve">2026-10-15T11:19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,15 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -181,15 +187,30 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
     <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -199,6 +220,24 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -265,6 +304,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -298,6 +352,15 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
@@ -331,252 +394,282 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4479783873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Monitoring, Databases, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-jobgether-4477100901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPD Hosting LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
@@ -589,7 +682,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">Software Engineer – Graduate Program (Bootcamp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-%E2%80%93-graduate-program-bootcamp-at-palo-alto-networks-4476680286</t>
   </si>
   <si>
     <t xml:space="preserve">Sela</t>
@@ -619,9 +721,6 @@
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
   </si>
   <si>
@@ -637,6 +736,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Recovery Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8887212002</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -700,157 +814,145 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -983,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -999,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1081,7 +1183,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1089,7 +1191,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1097,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1109,36 +1211,52 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3">
-        <v>29</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>7</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1151,7 +1269,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1163,34 +1281,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1198,31 +1316,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1230,13 +1348,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>25</v>
@@ -1245,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1262,31 +1380,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1294,13 +1412,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1309,16 +1427,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1326,31 +1444,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1358,31 +1476,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1390,31 +1508,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
+        <v>96</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1422,31 +1540,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -1454,31 +1572,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1486,31 +1604,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -1518,31 +1636,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1550,31 +1668,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1582,31 +1700,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1614,31 +1732,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3">
-        <v>57</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1646,31 +1764,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>68</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>51</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -1678,25 +1796,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>129</v>
@@ -1722,19 +1840,19 @@
         <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -1742,7 +1860,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>137</v>
@@ -1751,22 +1869,22 @@
         <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1774,31 +1892,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1806,31 +1924,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -1838,31 +1956,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1870,31 +1988,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
@@ -1902,31 +2020,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -1934,31 +2052,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
@@ -1966,31 +2084,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2147,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2043,83 +2161,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
@@ -2128,68 +2246,68 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2198,433 +2316,433 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
+        <v>96</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K11" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="K14" s="3">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>70</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="3">
-        <v>57</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>129</v>
@@ -2633,7 +2751,7 @@
         <v>130</v>
       </c>
       <c r="K17" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -2650,30 +2768,30 @@
         <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="K18" s="3">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>137</v>
@@ -2682,200 +2800,200 @@
         <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K21" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="K22" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="K24" s="3">
         <v>56</v>
@@ -2883,77 +3001,77 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>183</v>
@@ -2962,235 +3080,235 @@
         <v>184</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K30" s="3">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="K32" s="3">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="K33" s="3">
         <v>1</v>
@@ -3198,208 +3316,422 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="K34" s="3">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="K35" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>223</v>
+        <v>79</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G36" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>227</v>
+        <v>50</v>
       </c>
       <c r="K36" s="3">
-        <v>77</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G37" s="3" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>160</v>
+        <v>233</v>
       </c>
       <c r="K37" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G38" s="3" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K38" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K39" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K40" s="3">
         <v>0</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="K39" s="3">
-        <v>70</v>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K43" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="K44" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K45" s="3">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K45"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3439,6 +3771,12 @@
     <hyperlink ref="I37" r:id="rId36"/>
     <hyperlink ref="I38" r:id="rId37"/>
     <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3446,9 +3784,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3457,102 +3795,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3567,178 +3929,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3755,13 +4117,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
@@ -3769,10 +4131,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -3780,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4">
@@ -3791,10 +4153,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
@@ -3805,7 +4167,29 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>275</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3823,51 +4207,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-latest.xlsx
+++ b/reports/devops-juniors-israel-latest.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-15T11:19:53</t>
+    <t xml:space="preserve">2026-10-16T11:15:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -376,6 +376,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -394,6 +412,24 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -448,9 +484,6 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
@@ -460,6 +493,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Developer, Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppCard, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-developer-core-platform-at-appcard-inc-4477317181</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -505,7 +553,22 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-07</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">Gini-Apps</t>
@@ -547,24 +610,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
@@ -595,21 +640,6 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -718,37 +748,25 @@
     <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recovery Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8887212002</t>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
@@ -757,9 +775,6 @@
     <t xml:space="preserve">Global-e</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
   </si>
   <si>
@@ -814,21 +829,6 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -853,13 +853,19 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -871,30 +877,24 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -928,19 +928,19 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1085,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1101,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1199,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1207,7 +1207,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1241,7 +1241,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -1249,7 +1249,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1257,7 +1257,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1268,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1325,7 +1325,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1389,7 +1389,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1645,7 +1645,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
         <v>83</v>
@@ -1709,7 +1709,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>74</v>
@@ -1741,7 +1741,7 @@
         <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
         <v>70</v>
@@ -1773,16 +1773,16 @@
         <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -1802,25 +1802,25 @@
         <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -1828,31 +1828,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
@@ -1860,31 +1860,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1892,31 +1892,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
@@ -1936,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>151</v>
@@ -1948,7 +1948,7 @@
         <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1956,31 +1956,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -1988,31 +1988,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>161</v>
+        <v>162<